--- a/servers/maze_main_server/conf.d/data/maze_equip_affix_roll_type_v8【迷宫-装备-词条值随机范围】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_equip_affix_roll_type_v8【迷宫-装备-词条值随机范围】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\新建文件夹\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A553068-B9ED-4FC5-820E-7263B5771720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FF22B6-DA08-4288-A9CC-DC060647FB7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_equip_affix_roll_type_v8" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -120,10 +120,6 @@
   </si>
   <si>
     <t>抗性</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>随机词条百万分比</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -400,7 +396,6 @@
       <sheetName val="联盟光辉等级"/>
       <sheetName val="堡垒战规则确认"/>
       <sheetName val="功勋获得"/>
-      <sheetName val="4.0数据提交202301~202306"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -589,7 +584,6 @@
       <sheetData sheetId="136"/>
       <sheetData sheetId="137"/>
       <sheetData sheetId="138"/>
-      <sheetData sheetId="139"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -873,7 +867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J292"/>
+  <dimension ref="A1:J290"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.125" style="1" customWidth="1"/>
@@ -882,7 +876,7 @@
     <col min="5" max="5" width="11.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="13" style="1" customWidth="1"/>
     <col min="7" max="8" width="19.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="42.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.625" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3110,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="H75" s="6">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I75" s="6">
         <v>1</v>
@@ -9143,7 +9137,7 @@
         <v>10000</v>
       </c>
       <c r="I276" s="3">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="J276" s="2" t="s">
         <v>24</v>
@@ -9175,7 +9169,7 @@
         <v>10000</v>
       </c>
       <c r="I277" s="3">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="J277" s="2" t="s">
         <v>24</v>
@@ -9595,70 +9589,6 @@
       </c>
       <c r="J290" s="2" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="291" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A291">
-        <v>10301</v>
-      </c>
-      <c r="B291">
-        <v>103</v>
-      </c>
-      <c r="C291" s="3">
-        <v>0</v>
-      </c>
-      <c r="D291" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="E291" s="3">
-        <v>1</v>
-      </c>
-      <c r="F291" s="3">
-        <v>100</v>
-      </c>
-      <c r="G291" s="3">
-        <v>0</v>
-      </c>
-      <c r="H291" s="3">
-        <v>10000</v>
-      </c>
-      <c r="I291" s="3">
-        <v>10000</v>
-      </c>
-      <c r="J291" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="292" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A292">
-        <v>10302</v>
-      </c>
-      <c r="B292">
-        <v>103</v>
-      </c>
-      <c r="C292" s="3">
-        <v>0</v>
-      </c>
-      <c r="D292" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="E292" s="3">
-        <v>1</v>
-      </c>
-      <c r="F292" s="3">
-        <v>5</v>
-      </c>
-      <c r="G292" s="3">
-        <v>10000</v>
-      </c>
-      <c r="H292" s="3">
-        <v>10000</v>
-      </c>
-      <c r="I292" s="3">
-        <v>10000</v>
-      </c>
-      <c r="J292" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_equip_affix_roll_type_v8【迷宫-装备-词条值随机范围】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_equip_affix_roll_type_v8【迷宫-装备-词条值随机范围】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5FC8B6-5407-46E2-A60F-E3788A11D295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A553068-B9ED-4FC5-820E-7263B5771720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_equip_affix_roll_type_v8" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -120,6 +120,10 @@
   </si>
   <si>
     <t>抗性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机词条百万分比</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -396,6 +400,7 @@
       <sheetName val="联盟光辉等级"/>
       <sheetName val="堡垒战规则确认"/>
       <sheetName val="功勋获得"/>
+      <sheetName val="4.0数据提交202301~202306"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -584,6 +589,7 @@
       <sheetData sheetId="136"/>
       <sheetData sheetId="137"/>
       <sheetData sheetId="138"/>
+      <sheetData sheetId="139"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -867,7 +873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J290"/>
+  <dimension ref="A1:J292"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.125" style="1" customWidth="1"/>
@@ -876,7 +882,7 @@
     <col min="5" max="5" width="11.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="13" style="1" customWidth="1"/>
     <col min="7" max="8" width="19.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="42.25" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -9589,6 +9595,70 @@
       </c>
       <c r="J290" s="2" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A291">
+        <v>10301</v>
+      </c>
+      <c r="B291">
+        <v>103</v>
+      </c>
+      <c r="C291" s="3">
+        <v>0</v>
+      </c>
+      <c r="D291" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="E291" s="3">
+        <v>1</v>
+      </c>
+      <c r="F291" s="3">
+        <v>100</v>
+      </c>
+      <c r="G291" s="3">
+        <v>0</v>
+      </c>
+      <c r="H291" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I291" s="3">
+        <v>10000</v>
+      </c>
+      <c r="J291" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A292">
+        <v>10302</v>
+      </c>
+      <c r="B292">
+        <v>103</v>
+      </c>
+      <c r="C292" s="3">
+        <v>0</v>
+      </c>
+      <c r="D292" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="E292" s="3">
+        <v>1</v>
+      </c>
+      <c r="F292" s="3">
+        <v>5</v>
+      </c>
+      <c r="G292" s="3">
+        <v>10000</v>
+      </c>
+      <c r="H292" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I292" s="3">
+        <v>10000</v>
+      </c>
+      <c r="J292" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_equip_affix_roll_type_v8【迷宫-装备-词条值随机范围】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_equip_affix_roll_type_v8【迷宫-装备-词条值随机范围】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\新建文件夹\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FF22B6-DA08-4288-A9CC-DC060647FB7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A553068-B9ED-4FC5-820E-7263B5771720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_equip_affix_roll_type_v8" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -120,6 +120,10 @@
   </si>
   <si>
     <t>抗性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机词条百万分比</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -396,6 +400,7 @@
       <sheetName val="联盟光辉等级"/>
       <sheetName val="堡垒战规则确认"/>
       <sheetName val="功勋获得"/>
+      <sheetName val="4.0数据提交202301~202306"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -584,6 +589,7 @@
       <sheetData sheetId="136"/>
       <sheetData sheetId="137"/>
       <sheetData sheetId="138"/>
+      <sheetData sheetId="139"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -867,7 +873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J290"/>
+  <dimension ref="A1:J292"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.125" style="1" customWidth="1"/>
@@ -876,7 +882,7 @@
     <col min="5" max="5" width="11.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="13" style="1" customWidth="1"/>
     <col min="7" max="8" width="19.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="42.25" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3104,7 +3110,7 @@
         <v>0</v>
       </c>
       <c r="H75" s="6">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I75" s="6">
         <v>1</v>
@@ -9137,7 +9143,7 @@
         <v>10000</v>
       </c>
       <c r="I276" s="3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J276" s="2" t="s">
         <v>24</v>
@@ -9169,7 +9175,7 @@
         <v>10000</v>
       </c>
       <c r="I277" s="3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J277" s="2" t="s">
         <v>24</v>
@@ -9589,6 +9595,70 @@
       </c>
       <c r="J290" s="2" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A291">
+        <v>10301</v>
+      </c>
+      <c r="B291">
+        <v>103</v>
+      </c>
+      <c r="C291" s="3">
+        <v>0</v>
+      </c>
+      <c r="D291" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="E291" s="3">
+        <v>1</v>
+      </c>
+      <c r="F291" s="3">
+        <v>100</v>
+      </c>
+      <c r="G291" s="3">
+        <v>0</v>
+      </c>
+      <c r="H291" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I291" s="3">
+        <v>10000</v>
+      </c>
+      <c r="J291" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A292">
+        <v>10302</v>
+      </c>
+      <c r="B292">
+        <v>103</v>
+      </c>
+      <c r="C292" s="3">
+        <v>0</v>
+      </c>
+      <c r="D292" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="E292" s="3">
+        <v>1</v>
+      </c>
+      <c r="F292" s="3">
+        <v>5</v>
+      </c>
+      <c r="G292" s="3">
+        <v>10000</v>
+      </c>
+      <c r="H292" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I292" s="3">
+        <v>10000</v>
+      </c>
+      <c r="J292" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
